--- a/data/trans_orig/P57_R-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/P57_R-Estudios-trans_orig.xlsx
@@ -536,7 +536,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con autopercepción de la felicidad menor o igual a 6 (Likert 0 a 10) en 2016</t>
+          <t>Población con autopercepción de la felicidad menor o igual a 6 (Likert 0 a 10) en 2016 (tasa de respuesta: 99,57%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -731,12 +731,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>202909</t>
+          <t>205465</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>252653</t>
+          <t>254817</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -746,12 +746,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>26,97%</t>
+          <t>27,31%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>33,59%</t>
+          <t>33,87%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -766,12 +766,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>354566</t>
+          <t>354107</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>416353</t>
+          <t>418380</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -781,12 +781,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>35,78%</t>
+          <t>35,73%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>42,01%</t>
+          <t>42,22%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -801,12 +801,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>571381</t>
+          <t>571054</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>655066</t>
+          <t>655249</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -816,12 +816,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>32,78%</t>
+          <t>32,76%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>37,58%</t>
+          <t>37,59%</t>
         </is>
       </c>
     </row>
@@ -844,12 +844,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>499579</t>
+          <t>497415</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>549323</t>
+          <t>546767</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -859,12 +859,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>66,41%</t>
+          <t>66,13%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>73,03%</t>
+          <t>72,69%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -879,12 +879,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>574626</t>
+          <t>572599</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>636413</t>
+          <t>636872</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -894,12 +894,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>57,99%</t>
+          <t>57,78%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>64,22%</t>
+          <t>64,27%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -914,12 +914,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1088145</t>
+          <t>1087962</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1171830</t>
+          <t>1172157</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -929,12 +929,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>62,42%</t>
+          <t>62,41%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>67,22%</t>
+          <t>67,24%</t>
         </is>
       </c>
     </row>
@@ -1074,12 +1074,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>299821</t>
+          <t>301237</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>370463</t>
+          <t>368541</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1089,12 +1089,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>14,51%</t>
+          <t>14,57%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>17,92%</t>
+          <t>17,83%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1109,12 +1109,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>351268</t>
+          <t>356384</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>423256</t>
+          <t>425936</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1124,12 +1124,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>17,75%</t>
+          <t>18,01%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>21,39%</t>
+          <t>21,53%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1144,12 +1144,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>674329</t>
+          <t>669153</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>770985</t>
+          <t>770544</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1159,12 +1159,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>16,67%</t>
+          <t>16,54%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>19,06%</t>
+          <t>19,05%</t>
         </is>
       </c>
     </row>
@@ -1187,12 +1187,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1696371</t>
+          <t>1698293</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1767013</t>
+          <t>1765597</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1202,12 +1202,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>82,08%</t>
+          <t>82,17%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>85,49%</t>
+          <t>85,43%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1222,12 +1222,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>1555501</t>
+          <t>1552821</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>1627489</t>
+          <t>1622373</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1237,12 +1237,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>78,61%</t>
+          <t>78,47%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>82,25%</t>
+          <t>81,99%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1257,12 +1257,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>3274607</t>
+          <t>3275048</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>3371263</t>
+          <t>3376439</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1272,12 +1272,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>80,94%</t>
+          <t>80,95%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>83,33%</t>
+          <t>83,46%</t>
         </is>
       </c>
     </row>
@@ -1417,12 +1417,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>47520</t>
+          <t>45856</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>78975</t>
+          <t>76352</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1432,12 +1432,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>8,72%</t>
+          <t>8,41%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>14,49%</t>
+          <t>14,01%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1452,12 +1452,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>35848</t>
+          <t>38147</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>63853</t>
+          <t>65529</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1467,12 +1467,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>6,57%</t>
+          <t>6,99%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>11,7%</t>
+          <t>12,0%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1487,12 +1487,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>92640</t>
+          <t>91473</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>133882</t>
+          <t>131902</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1502,12 +1502,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>8,49%</t>
+          <t>8,39%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>12,27%</t>
+          <t>12,09%</t>
         </is>
       </c>
     </row>
@@ -1530,12 +1530,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>465959</t>
+          <t>468582</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>497414</t>
+          <t>499078</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1545,12 +1545,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>85,51%</t>
+          <t>85,99%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>91,28%</t>
+          <t>91,59%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1565,12 +1565,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>482073</t>
+          <t>480397</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>510078</t>
+          <t>507779</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1580,12 +1580,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>88,3%</t>
+          <t>88,0%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>93,43%</t>
+          <t>93,01%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1600,12 +1600,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>956978</t>
+          <t>958958</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>998220</t>
+          <t>999387</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1615,12 +1615,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>87,73%</t>
+          <t>87,91%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>91,51%</t>
+          <t>91,61%</t>
         </is>
       </c>
     </row>
@@ -1760,12 +1760,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>579798</t>
+          <t>576623</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>667515</t>
+          <t>666498</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1775,12 +1775,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>17,24%</t>
+          <t>17,14%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>19,84%</t>
+          <t>19,81%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1795,12 +1795,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>769112</t>
+          <t>770165</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>871063</t>
+          <t>873325</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1810,12 +1810,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>21,88%</t>
+          <t>21,91%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>24,78%</t>
+          <t>24,84%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1830,12 +1830,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>1378317</t>
+          <t>1375106</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>1520852</t>
+          <t>1512121</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1845,12 +1845,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>20,03%</t>
+          <t>19,99%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>22,11%</t>
+          <t>21,98%</t>
         </is>
       </c>
     </row>
@@ -1873,12 +1873,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>2696485</t>
+          <t>2697502</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>2784202</t>
+          <t>2787377</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1888,12 +1888,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>80,16%</t>
+          <t>80,19%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>82,76%</t>
+          <t>82,86%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1908,12 +1908,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>2644599</t>
+          <t>2642337</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>2746550</t>
+          <t>2745497</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1923,12 +1923,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>75,22%</t>
+          <t>75,16%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>78,12%</t>
+          <t>78,09%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1943,12 +1943,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>5358810</t>
+          <t>5367541</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>5501345</t>
+          <t>5504556</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1958,12 +1958,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>77,89%</t>
+          <t>78,02%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>79,97%</t>
+          <t>80,01%</t>
         </is>
       </c>
     </row>
@@ -2139,7 +2139,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con autopercepción de la felicidad menor o igual a 6 (Likert 0 a 10) en 2023</t>
+          <t>Población con autopercepción de la felicidad menor o igual a 6 (Likert 0 a 10) en 2023 (tasa de respuesta: 99,4%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -2334,12 +2334,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>131139</t>
+          <t>129669</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>167716</t>
+          <t>166965</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -2349,12 +2349,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>25,85%</t>
+          <t>25,56%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>33,06%</t>
+          <t>32,91%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -2369,12 +2369,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>252543</t>
+          <t>251487</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>290687</t>
+          <t>291650</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -2384,12 +2384,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>33,98%</t>
+          <t>33,84%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>39,11%</t>
+          <t>39,24%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -2404,12 +2404,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>392920</t>
+          <t>388043</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>444890</t>
+          <t>443808</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -2419,12 +2419,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>31,42%</t>
+          <t>31,03%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>35,58%</t>
+          <t>35,49%</t>
         </is>
       </c>
     </row>
@@ -2447,12 +2447,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>339640</t>
+          <t>340391</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>376217</t>
+          <t>377687</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -2462,12 +2462,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>66,94%</t>
+          <t>67,09%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>74,15%</t>
+          <t>74,44%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -2482,12 +2482,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>452476</t>
+          <t>451513</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>490620</t>
+          <t>491676</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -2497,12 +2497,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>60,89%</t>
+          <t>60,76%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>66,02%</t>
+          <t>66,16%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -2517,12 +2517,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>805630</t>
+          <t>806712</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>857600</t>
+          <t>862477</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -2532,12 +2532,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>64,42%</t>
+          <t>64,51%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>68,58%</t>
+          <t>68,97%</t>
         </is>
       </c>
     </row>
@@ -2677,12 +2677,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>152459</t>
+          <t>155615</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>259949</t>
+          <t>265314</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -2692,12 +2692,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>6,66%</t>
+          <t>6,8%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>11,36%</t>
+          <t>11,59%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -2712,12 +2712,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>180185</t>
+          <t>180102</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>287943</t>
+          <t>286706</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -2727,12 +2727,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>8,08%</t>
+          <t>8,07%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>12,91%</t>
+          <t>12,85%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -2747,12 +2747,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>381681</t>
+          <t>373569</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>531592</t>
+          <t>529882</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -2762,12 +2762,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>8,45%</t>
+          <t>8,27%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>11,76%</t>
+          <t>11,72%</t>
         </is>
       </c>
     </row>
@@ -2790,12 +2790,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>2028396</t>
+          <t>2023031</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>2135886</t>
+          <t>2132730</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -2805,12 +2805,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>88,64%</t>
+          <t>88,41%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>93,34%</t>
+          <t>93,2%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -2825,12 +2825,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>1943262</t>
+          <t>1944499</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>2051020</t>
+          <t>2051103</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -2840,12 +2840,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>87,09%</t>
+          <t>87,15%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>91,92%</t>
+          <t>91,93%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -2860,12 +2860,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>3987959</t>
+          <t>3989669</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>4137870</t>
+          <t>4145982</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -2875,12 +2875,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>88,24%</t>
+          <t>88,28%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>91,55%</t>
+          <t>91,73%</t>
         </is>
       </c>
     </row>
@@ -3020,12 +3020,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>42257</t>
+          <t>43586</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>72750</t>
+          <t>73055</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -3035,12 +3035,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>6,54%</t>
+          <t>6,75%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>11,26%</t>
+          <t>11,31%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -3055,12 +3055,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>43116</t>
+          <t>43396</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>66939</t>
+          <t>68302</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -3070,47 +3070,47 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>6,55%</t>
+          <t>6,59%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
+          <t>10,37%</t>
+        </is>
+      </c>
+      <c r="Q10" s="2" t="inlineStr">
+        <is>
+          <t>151</t>
+        </is>
+      </c>
+      <c r="R10" s="2" t="inlineStr">
+        <is>
+          <t>111782</t>
+        </is>
+      </c>
+      <c r="S10" s="2" t="inlineStr">
+        <is>
+          <t>95756</t>
+        </is>
+      </c>
+      <c r="T10" s="2" t="inlineStr">
+        <is>
+          <t>132601</t>
+        </is>
+      </c>
+      <c r="U10" s="2" t="inlineStr">
+        <is>
+          <t>8,57%</t>
+        </is>
+      </c>
+      <c r="V10" s="2" t="inlineStr">
+        <is>
+          <t>7,34%</t>
+        </is>
+      </c>
+      <c r="W10" s="2" t="inlineStr">
+        <is>
           <t>10,17%</t>
-        </is>
-      </c>
-      <c r="Q10" s="2" t="inlineStr">
-        <is>
-          <t>151</t>
-        </is>
-      </c>
-      <c r="R10" s="2" t="inlineStr">
-        <is>
-          <t>111782</t>
-        </is>
-      </c>
-      <c r="S10" s="2" t="inlineStr">
-        <is>
-          <t>93872</t>
-        </is>
-      </c>
-      <c r="T10" s="2" t="inlineStr">
-        <is>
-          <t>130621</t>
-        </is>
-      </c>
-      <c r="U10" s="2" t="inlineStr">
-        <is>
-          <t>8,57%</t>
-        </is>
-      </c>
-      <c r="V10" s="2" t="inlineStr">
-        <is>
-          <t>7,2%</t>
-        </is>
-      </c>
-      <c r="W10" s="2" t="inlineStr">
-        <is>
-          <t>10,01%</t>
         </is>
       </c>
     </row>
@@ -3133,12 +3133,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>573253</t>
+          <t>572948</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>603746</t>
+          <t>602417</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -3148,12 +3148,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>88,74%</t>
+          <t>88,69%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>93,46%</t>
+          <t>93,25%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -3168,12 +3168,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>591531</t>
+          <t>590168</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>615354</t>
+          <t>615074</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -3183,47 +3183,47 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
+          <t>89,63%</t>
+        </is>
+      </c>
+      <c r="P11" s="2" t="inlineStr">
+        <is>
+          <t>93,41%</t>
+        </is>
+      </c>
+      <c r="Q11" s="2" t="inlineStr">
+        <is>
+          <t>1530</t>
+        </is>
+      </c>
+      <c r="R11" s="2" t="inlineStr">
+        <is>
+          <t>1192692</t>
+        </is>
+      </c>
+      <c r="S11" s="2" t="inlineStr">
+        <is>
+          <t>1171873</t>
+        </is>
+      </c>
+      <c r="T11" s="2" t="inlineStr">
+        <is>
+          <t>1208718</t>
+        </is>
+      </c>
+      <c r="U11" s="2" t="inlineStr">
+        <is>
+          <t>91,43%</t>
+        </is>
+      </c>
+      <c r="V11" s="2" t="inlineStr">
+        <is>
           <t>89,83%</t>
         </is>
       </c>
-      <c r="P11" s="2" t="inlineStr">
-        <is>
-          <t>93,45%</t>
-        </is>
-      </c>
-      <c r="Q11" s="2" t="inlineStr">
-        <is>
-          <t>1530</t>
-        </is>
-      </c>
-      <c r="R11" s="2" t="inlineStr">
-        <is>
-          <t>1192692</t>
-        </is>
-      </c>
-      <c r="S11" s="2" t="inlineStr">
-        <is>
-          <t>1173853</t>
-        </is>
-      </c>
-      <c r="T11" s="2" t="inlineStr">
-        <is>
-          <t>1210602</t>
-        </is>
-      </c>
-      <c r="U11" s="2" t="inlineStr">
-        <is>
-          <t>91,43%</t>
-        </is>
-      </c>
-      <c r="V11" s="2" t="inlineStr">
-        <is>
-          <t>89,99%</t>
-        </is>
-      </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>92,8%</t>
+          <t>92,66%</t>
         </is>
       </c>
     </row>
@@ -3363,12 +3363,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>332307</t>
+          <t>331848</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>478277</t>
+          <t>479589</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -3378,12 +3378,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>9,66%</t>
+          <t>9,64%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>13,9%</t>
+          <t>13,93%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -3398,12 +3398,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>463279</t>
+          <t>470926</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>626063</t>
+          <t>624131</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -3413,12 +3413,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>12,75%</t>
+          <t>12,96%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>17,23%</t>
+          <t>17,18%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -3433,12 +3433,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>841638</t>
+          <t>858581</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>1076191</t>
+          <t>1077260</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3448,12 +3448,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>11,9%</t>
+          <t>12,14%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>15,21%</t>
+          <t>15,23%</t>
         </is>
       </c>
     </row>
@@ -3476,12 +3476,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>2963428</t>
+          <t>2962116</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>3109398</t>
+          <t>3109857</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -3491,12 +3491,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>86,1%</t>
+          <t>86,07%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>90,34%</t>
+          <t>90,36%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -3511,12 +3511,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>3006776</t>
+          <t>3008708</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>3169560</t>
+          <t>3161913</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -3526,12 +3526,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>82,77%</t>
+          <t>82,82%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>87,25%</t>
+          <t>87,04%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -3546,12 +3546,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>5998353</t>
+          <t>5997284</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>6232906</t>
+          <t>6215963</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -3561,12 +3561,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>84,79%</t>
+          <t>84,77%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>88,1%</t>
+          <t>87,86%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P57_R-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/P57_R-Estudios-trans_orig.xlsx
@@ -731,12 +731,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>205465</t>
+          <t>203524</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>254817</t>
+          <t>253584</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -746,12 +746,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>27,31%</t>
+          <t>27,06%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>33,87%</t>
+          <t>33,71%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -766,12 +766,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>354107</t>
+          <t>353375</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>418380</t>
+          <t>418511</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -781,12 +781,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>35,73%</t>
+          <t>35,66%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>42,22%</t>
+          <t>42,23%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -801,12 +801,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>571054</t>
+          <t>574935</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>655249</t>
+          <t>655810</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -816,12 +816,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>32,76%</t>
+          <t>32,98%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>37,59%</t>
+          <t>37,62%</t>
         </is>
       </c>
     </row>
@@ -844,12 +844,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>497415</t>
+          <t>498648</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>546767</t>
+          <t>548708</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -859,12 +859,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>66,13%</t>
+          <t>66,29%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>72,69%</t>
+          <t>72,94%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -879,12 +879,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>572599</t>
+          <t>572468</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>636872</t>
+          <t>637604</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -894,12 +894,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>57,78%</t>
+          <t>57,77%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>64,27%</t>
+          <t>64,34%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -914,12 +914,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1087962</t>
+          <t>1087401</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1172157</t>
+          <t>1168276</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -929,12 +929,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>62,41%</t>
+          <t>62,38%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>67,24%</t>
+          <t>67,02%</t>
         </is>
       </c>
     </row>
@@ -1074,12 +1074,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>301237</t>
+          <t>300575</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>368541</t>
+          <t>369542</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1089,12 +1089,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>14,57%</t>
+          <t>14,54%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>17,83%</t>
+          <t>17,88%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1109,12 +1109,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>356384</t>
+          <t>355326</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>425936</t>
+          <t>425213</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1124,12 +1124,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>18,01%</t>
+          <t>17,96%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>21,53%</t>
+          <t>21,49%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1144,12 +1144,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>669153</t>
+          <t>672278</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>770544</t>
+          <t>780266</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1159,12 +1159,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>16,54%</t>
+          <t>16,62%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>19,05%</t>
+          <t>19,29%</t>
         </is>
       </c>
     </row>
@@ -1187,12 +1187,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1698293</t>
+          <t>1697292</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1765597</t>
+          <t>1766259</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1202,12 +1202,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>82,17%</t>
+          <t>82,12%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>85,43%</t>
+          <t>85,46%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1222,12 +1222,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>1552821</t>
+          <t>1553544</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>1622373</t>
+          <t>1623431</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1237,12 +1237,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>78,47%</t>
+          <t>78,51%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>81,99%</t>
+          <t>82,04%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1257,12 +1257,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>3275048</t>
+          <t>3265326</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>3376439</t>
+          <t>3373314</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1272,12 +1272,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>80,95%</t>
+          <t>80,71%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>83,46%</t>
+          <t>83,38%</t>
         </is>
       </c>
     </row>
@@ -1417,12 +1417,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>45856</t>
+          <t>47008</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>76352</t>
+          <t>77800</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1432,12 +1432,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>8,41%</t>
+          <t>8,63%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>14,01%</t>
+          <t>14,28%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1452,12 +1452,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>38147</t>
+          <t>36026</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>65529</t>
+          <t>66582</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1467,12 +1467,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>6,99%</t>
+          <t>6,6%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>12,0%</t>
+          <t>12,2%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1487,12 +1487,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>91473</t>
+          <t>91579</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>131902</t>
+          <t>134221</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1502,12 +1502,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>8,39%</t>
+          <t>8,4%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>12,09%</t>
+          <t>12,3%</t>
         </is>
       </c>
     </row>
@@ -1530,12 +1530,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>468582</t>
+          <t>467134</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>499078</t>
+          <t>497926</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1545,12 +1545,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>85,99%</t>
+          <t>85,72%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>91,59%</t>
+          <t>91,37%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1565,12 +1565,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>480397</t>
+          <t>479344</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>507779</t>
+          <t>509900</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1580,12 +1580,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>88,0%</t>
+          <t>87,8%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>93,01%</t>
+          <t>93,4%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1600,12 +1600,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>958958</t>
+          <t>956639</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>999387</t>
+          <t>999281</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1615,12 +1615,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>87,91%</t>
+          <t>87,7%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>91,61%</t>
+          <t>91,6%</t>
         </is>
       </c>
     </row>
@@ -1760,12 +1760,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>576623</t>
+          <t>583062</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>666498</t>
+          <t>672207</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1775,12 +1775,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>17,14%</t>
+          <t>17,33%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>19,81%</t>
+          <t>19,98%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1795,12 +1795,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>770165</t>
+          <t>770799</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>873325</t>
+          <t>874597</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1810,12 +1810,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>21,91%</t>
+          <t>21,92%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>24,84%</t>
+          <t>24,88%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1830,12 +1830,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>1375106</t>
+          <t>1367921</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>1512121</t>
+          <t>1512895</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1845,12 +1845,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>19,99%</t>
+          <t>19,88%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>21,98%</t>
+          <t>21,99%</t>
         </is>
       </c>
     </row>
@@ -1873,12 +1873,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>2697502</t>
+          <t>2691793</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>2787377</t>
+          <t>2780938</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1888,12 +1888,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>80,19%</t>
+          <t>80,02%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>82,86%</t>
+          <t>82,67%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1908,12 +1908,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>2642337</t>
+          <t>2641065</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>2745497</t>
+          <t>2744863</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1923,12 +1923,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>75,16%</t>
+          <t>75,12%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>78,09%</t>
+          <t>78,08%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1943,12 +1943,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>5367541</t>
+          <t>5366767</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>5504556</t>
+          <t>5511741</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1958,12 +1958,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>78,02%</t>
+          <t>78,01%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>80,01%</t>
+          <t>80,12%</t>
         </is>
       </c>
     </row>
@@ -2329,32 +2329,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>148042</t>
+          <t>161295</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>129669</t>
+          <t>142875</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>166965</t>
+          <t>181530</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>29,18%</t>
+          <t>28,28%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>25,56%</t>
+          <t>25,05%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>32,91%</t>
+          <t>31,83%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -2364,32 +2364,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>269794</t>
+          <t>296031</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>251487</t>
+          <t>276454</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>291650</t>
+          <t>317276</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>36,3%</t>
+          <t>36,57%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>33,84%</t>
+          <t>34,15%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>39,24%</t>
+          <t>39,19%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -2399,32 +2399,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>417836</t>
+          <t>457326</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>388043</t>
+          <t>427273</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>443808</t>
+          <t>483678</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>33,41%</t>
+          <t>33,14%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>31,03%</t>
+          <t>30,97%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>35,49%</t>
+          <t>35,05%</t>
         </is>
       </c>
     </row>
@@ -2442,32 +2442,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>359314</t>
+          <t>409022</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>340391</t>
+          <t>388787</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>377687</t>
+          <t>427442</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>70,82%</t>
+          <t>71,72%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>67,09%</t>
+          <t>68,17%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>74,44%</t>
+          <t>74,95%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -2477,32 +2477,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>473369</t>
+          <t>513498</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>451513</t>
+          <t>492253</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>491676</t>
+          <t>533075</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>63,7%</t>
+          <t>63,43%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>60,76%</t>
+          <t>60,81%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>66,16%</t>
+          <t>65,85%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -2512,32 +2512,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>832684</t>
+          <t>922520</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>806712</t>
+          <t>896168</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>862477</t>
+          <t>952573</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>66,59%</t>
+          <t>66,86%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>64,51%</t>
+          <t>64,95%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>68,97%</t>
+          <t>69,03%</t>
         </is>
       </c>
     </row>
@@ -2555,17 +2555,17 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>507356</t>
+          <t>570317</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>507356</t>
+          <t>570317</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>507356</t>
+          <t>570317</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -2590,17 +2590,17 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>743163</t>
+          <t>809529</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>743163</t>
+          <t>809529</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>743163</t>
+          <t>809529</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -2625,17 +2625,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>1250520</t>
+          <t>1379846</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>1250520</t>
+          <t>1379846</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>1250520</t>
+          <t>1379846</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -2672,32 +2672,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>223482</t>
+          <t>245396</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>155615</t>
+          <t>215099</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>265314</t>
+          <t>276090</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>9,77%</t>
+          <t>11,01%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>6,8%</t>
+          <t>9,65%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>11,59%</t>
+          <t>12,39%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -2707,32 +2707,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>245496</t>
+          <t>282397</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>180102</t>
+          <t>255095</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>286706</t>
+          <t>309998</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>11,0%</t>
+          <t>13,05%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>8,07%</t>
+          <t>11,79%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>12,85%</t>
+          <t>14,32%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -2742,32 +2742,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>468977</t>
+          <t>527793</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>373569</t>
+          <t>490279</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>529882</t>
+          <t>569914</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>10,38%</t>
+          <t>12,01%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>8,27%</t>
+          <t>11,16%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>11,72%</t>
+          <t>12,97%</t>
         </is>
       </c>
     </row>
@@ -2785,32 +2785,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>2064863</t>
+          <t>1983081</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>2023031</t>
+          <t>1952387</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>2132730</t>
+          <t>2013378</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>90,23%</t>
+          <t>88,99%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>88,41%</t>
+          <t>87,61%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>93,2%</t>
+          <t>90,35%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -2820,32 +2820,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>1985709</t>
+          <t>1882024</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>1944499</t>
+          <t>1854423</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>2051103</t>
+          <t>1909326</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>89,0%</t>
+          <t>86,95%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>87,15%</t>
+          <t>85,68%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>91,93%</t>
+          <t>88,21%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -2855,32 +2855,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>4050574</t>
+          <t>3865105</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>3989669</t>
+          <t>3822984</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>4145982</t>
+          <t>3902619</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>89,62%</t>
+          <t>87,99%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>88,28%</t>
+          <t>87,03%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>91,73%</t>
+          <t>88,84%</t>
         </is>
       </c>
     </row>
@@ -2898,17 +2898,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>2288345</t>
+          <t>2228477</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>2288345</t>
+          <t>2228477</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>2288345</t>
+          <t>2228477</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -2933,17 +2933,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>2231205</t>
+          <t>2164421</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>2231205</t>
+          <t>2164421</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>2231205</t>
+          <t>2164421</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -2968,17 +2968,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>4519551</t>
+          <t>4392898</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>4519551</t>
+          <t>4392898</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>4519551</t>
+          <t>4392898</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -3015,32 +3015,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>57168</t>
+          <t>63823</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>43586</t>
+          <t>48117</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>73055</t>
+          <t>83199</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>8,85%</t>
+          <t>8,98%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>6,75%</t>
+          <t>6,77%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>11,31%</t>
+          <t>11,7%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -3050,32 +3050,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>54613</t>
+          <t>61565</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>43396</t>
+          <t>49188</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>68302</t>
+          <t>75808</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>8,29%</t>
+          <t>8,4%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>6,59%</t>
+          <t>6,71%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>10,37%</t>
+          <t>10,35%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3085,32 +3085,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>111782</t>
+          <t>125389</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>95756</t>
+          <t>104387</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>132601</t>
+          <t>146237</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>8,57%</t>
+          <t>8,69%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>7,34%</t>
+          <t>7,23%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>10,17%</t>
+          <t>10,13%</t>
         </is>
       </c>
     </row>
@@ -3128,32 +3128,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>588835</t>
+          <t>647097</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>572948</t>
+          <t>627721</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>602417</t>
+          <t>662803</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>91,15%</t>
+          <t>91,02%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>88,69%</t>
+          <t>88,3%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>93,25%</t>
+          <t>93,23%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -3163,32 +3163,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>603857</t>
+          <t>671189</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>590168</t>
+          <t>656946</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>615074</t>
+          <t>683566</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>91,71%</t>
+          <t>91,6%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>89,63%</t>
+          <t>89,65%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>93,41%</t>
+          <t>93,29%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -3198,32 +3198,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>1192692</t>
+          <t>1318286</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1171873</t>
+          <t>1297438</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1208718</t>
+          <t>1339288</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>91,43%</t>
+          <t>91,31%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>89,83%</t>
+          <t>89,87%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>92,66%</t>
+          <t>92,77%</t>
         </is>
       </c>
     </row>
@@ -3241,17 +3241,17 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>646003</t>
+          <t>710920</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>646003</t>
+          <t>710920</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>646003</t>
+          <t>710920</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -3276,17 +3276,17 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>658470</t>
+          <t>732754</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>658470</t>
+          <t>732754</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>658470</t>
+          <t>732754</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -3311,17 +3311,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>1304474</t>
+          <t>1443675</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>1304474</t>
+          <t>1443675</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>1304474</t>
+          <t>1443675</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -3358,32 +3358,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>428692</t>
+          <t>470513</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>331848</t>
+          <t>430247</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>479589</t>
+          <t>514082</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>12,46%</t>
+          <t>13,41%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>9,64%</t>
+          <t>12,26%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>13,93%</t>
+          <t>14,65%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -3393,32 +3393,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>569903</t>
+          <t>639994</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>470926</t>
+          <t>600302</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>624131</t>
+          <t>676521</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>15,69%</t>
+          <t>17,27%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>12,96%</t>
+          <t>16,2%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>17,18%</t>
+          <t>18,25%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -3428,32 +3428,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>998594</t>
+          <t>1110507</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>858581</t>
+          <t>1050032</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>1077260</t>
+          <t>1161955</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>14,12%</t>
+          <t>15,39%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>12,14%</t>
+          <t>14,55%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>15,23%</t>
+          <t>16,1%</t>
         </is>
       </c>
     </row>
@@ -3471,32 +3471,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>3013013</t>
+          <t>3039201</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>2962116</t>
+          <t>2995632</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>3109857</t>
+          <t>3079467</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>87,54%</t>
+          <t>86,59%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>86,07%</t>
+          <t>85,35%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>90,36%</t>
+          <t>87,74%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -3506,32 +3506,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>3062936</t>
+          <t>3066710</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>3008708</t>
+          <t>3030183</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>3161913</t>
+          <t>3106402</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>84,31%</t>
+          <t>82,73%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>82,82%</t>
+          <t>81,75%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>87,04%</t>
+          <t>83,8%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -3541,32 +3541,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>6075950</t>
+          <t>6105911</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>5997284</t>
+          <t>6054463</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>6215963</t>
+          <t>6166386</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>85,88%</t>
+          <t>84,61%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>84,77%</t>
+          <t>83,9%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>87,86%</t>
+          <t>85,45%</t>
         </is>
       </c>
     </row>
@@ -3584,17 +3584,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>3441705</t>
+          <t>3509714</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>3441705</t>
+          <t>3509714</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>3441705</t>
+          <t>3509714</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -3619,17 +3619,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>3632839</t>
+          <t>3706704</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>3632839</t>
+          <t>3706704</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>3632839</t>
+          <t>3706704</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -3654,17 +3654,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>7074544</t>
+          <t>7216418</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>7074544</t>
+          <t>7216418</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>7074544</t>
+          <t>7216418</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
